--- a/3_Automation_Dashboard/SomSaiJai_Dashboard_B3_2026.xlsx
+++ b/3_Automation_Dashboard/SomSaiJai_Dashboard_B3_2026.xlsx
@@ -133,10 +133,10 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Jpan" typeface="ÃÂ¯ÃÂ¼ÃÂ­ÃÂ¯ÃÂ¼ÃÂ³ ÃÂ¯ÃÂ¼ÃÂ°ÃÂ£ÃÂÃÂ´ÃÂ£ÃÂÃÂ·ÃÂ£ÃÂÃÂÃÂ£ÃÂÃÂ¯"/>
+        <a:font script="Hang" typeface="ÃÂ«ÃÂ§ÃÂÃÂ¬ÃÂÃÂ ÃÂªÃÂ³ÃÂ ÃÂ«ÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂ¥ÃÂ®ÃÂÃÂ¤ÃÂ½ÃÂ"/>
+        <a:font script="Hant" typeface="ÃÂ¦ÃÂÃÂ°ÃÂ§ÃÂ´ÃÂ°ÃÂ¦ÃÂÃÂÃÂ©ÃÂ«ÃÂ"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -168,10 +168,10 @@
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Jpan" typeface="ÃÂ¯ÃÂ¼ÃÂ­ÃÂ¯ÃÂ¼ÃÂ³ ÃÂ¯ÃÂ¼ÃÂ°ÃÂ£ÃÂÃÂ´ÃÂ£ÃÂÃÂ·ÃÂ£ÃÂÃÂÃÂ£ÃÂÃÂ¯"/>
+        <a:font script="Hang" typeface="ÃÂ«ÃÂ§ÃÂÃÂ¬ÃÂÃÂ ÃÂªÃÂ³ÃÂ ÃÂ«ÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂ¥ÃÂ®ÃÂÃÂ¤ÃÂ½ÃÂ"/>
+        <a:font script="Hant" typeface="ÃÂ¦ÃÂÃÂ°ÃÂ§ÃÂ´ÃÂ°ÃÂ¦ÃÂÃÂÃÂ©ÃÂ«ÃÂ"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -2773,7 +2773,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F23"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2890,9 +2890,309 @@
         <v>4000</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>03/09/2026</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Aug26</v>
+      </c>
+      <c r="C9" t="str">
+        <v>OPEX</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Salary</v>
+      </c>
+      <c r="E9" t="str">
+        <v>เงินเดือนพนักงาน ส.ค. (owner allocation from pooled transfers 25/26/27)</v>
+      </c>
+      <c r="F9">
+        <v>39000</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>13/08/2026</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Aug26</v>
+      </c>
+      <c r="C10" t="str">
+        <v>OPEX</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Salary</v>
+      </c>
+      <c r="E10" t="str">
+        <v>B3 Aug pre-salary: arkar 3,000 + HtunKyaw 2,000</v>
+      </c>
+      <c r="F10">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>04/08/2026</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Aug26</v>
+      </c>
+      <c r="C11" t="str">
+        <v>OPEX</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Salary</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Ming manager wage Aug (1/3 of ฿20,000; slips 98+64)</v>
+      </c>
+      <c r="F11">
+        <v>6666.66</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>24/08/2026</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Aug26</v>
+      </c>
+      <c r="C12" t="str">
+        <v>OPEX</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Other OPEX</v>
+      </c>
+      <c r="E12" t="str">
+        <v>เครื่องสกัดเย็น 1,142 + เต็นท์ 1,923 (1/3 equal split)</v>
+      </c>
+      <c r="F12">
+        <v>1021.66</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>29/08/2026</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Aug26</v>
+      </c>
+      <c r="C13" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Other</v>
+      </c>
+      <c r="E13" t="str">
+        <v>ค่าใช้จ่ายดำเนินงาน (ผู้จัดการซื้อ, ไม่มีบันทึกในสลิป) (1/3 equal split)</v>
+      </c>
+      <c r="F13">
+        <v>792.33</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>04/08/2026</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Aug26</v>
+      </c>
+      <c r="C14" t="str">
+        <v>OPEX</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Salary</v>
+      </c>
+      <c r="E14" t="str">
+        <v>Salary trainee: k 800, chang 1,200, mai 400 (1/3 equal split)</v>
+      </c>
+      <c r="F14">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>08/08/2026</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Aug26</v>
+      </c>
+      <c r="C15" t="str">
+        <v>OPEX</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Salary</v>
+      </c>
+      <c r="E15" t="str">
+        <v>Salary special event 1 person (1/3 equal split)</v>
+      </c>
+      <c r="F15">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>30/08/2026</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Aug26</v>
+      </c>
+      <c r="C16" t="str">
+        <v>OPEX</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Other OPEX</v>
+      </c>
+      <c r="E16" t="str">
+        <v>ค่าปริ้นเอกสาร (1/3 equal split)</v>
+      </c>
+      <c r="F16">
+        <v>63.33</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>21/08/2026</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Aug26</v>
+      </c>
+      <c r="C17" t="str">
+        <v>OPEX</v>
+      </c>
+      <c r="D17" t="str">
+        <v>Other OPEX</v>
+      </c>
+      <c r="E17" t="str">
+        <v>ป้าย QR code ใหม่ 4 อัน (1/3 equal split)</v>
+      </c>
+      <c r="F17">
+        <v>48.33</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>03/08/2026</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Aug26</v>
+      </c>
+      <c r="C18" t="str">
+        <v>OPEX</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="E18" t="str">
+        <v>ค่าเช่า stock เดือน august (1/3 split)</v>
+      </c>
+      <c r="F18">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>21/08/2026</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Aug26</v>
+      </c>
+      <c r="C19" t="str">
+        <v>OPEX</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="E19" t="str">
+        <v>ค่าเช่า B3 เดือน august (MWA01)</v>
+      </c>
+      <c r="F19">
+        <v>18780.22</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>04/08/2026</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Aug26</v>
+      </c>
+      <c r="C20" t="str">
+        <v>OPEX</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Other OPEX</v>
+      </c>
+      <c r="E20" t="str">
+        <v>B3 washing fee</v>
+      </c>
+      <c r="F20">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>03/08/2026</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Aug26</v>
+      </c>
+      <c r="C21" t="str">
+        <v>OPEX</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Other OPEX</v>
+      </c>
+      <c r="E21" t="str">
+        <v>ค่ายกของ (1/3 equal split)</v>
+      </c>
+      <c r="F21">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>06/08/2026</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Aug26</v>
+      </c>
+      <c r="C22" t="str">
+        <v>OPEX</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Other OPEX</v>
+      </c>
+      <c r="E22" t="str">
+        <v>กล้องวงจรปิด 1 ตัว</v>
+      </c>
+      <c r="F22">
+        <v>1495.5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>01/08/2026</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Jul26</v>
+      </c>
+      <c r="C23" t="str">
+        <v>OPEX</v>
+      </c>
+      <c r="D23" t="str">
+        <v>Salary</v>
+      </c>
+      <c r="E23" t="str">
+        <v>Salary B3 7 days (จ่าย 01/08 — เจ้าของระบุเป็นค่าใช้จ่ายเดือน ก.ค.)</v>
+      </c>
+      <c r="F23">
+        <v>3500</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F23"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3547,7 +3847,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AD2"/>
+  <dimension ref="A1:AE33"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3645,10 +3945,633 @@
       <c r="AD2" t="str">
         <v>Used Young Coco</v>
       </c>
+      <c r="AE2" t="str">
+        <v>Source Note</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>01/08/2026</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Sat</v>
+      </c>
+      <c r="C3">
+        <v>8562</v>
+      </c>
+      <c r="D3">
+        <v>6189</v>
+      </c>
+      <c r="G3">
+        <v>2373</v>
+      </c>
+      <c r="AE3" t="str">
+        <v>POS export somsaijai-2026-08-01-to-31.json</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>02/08/2026</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Sun</v>
+      </c>
+      <c r="C4">
+        <v>10444</v>
+      </c>
+      <c r="D4">
+        <v>8687</v>
+      </c>
+      <c r="G4">
+        <v>1757</v>
+      </c>
+      <c r="AE4" t="str">
+        <v>POS export somsaijai-2026-08-01-to-31.json</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>03/08/2026</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Mon</v>
+      </c>
+      <c r="C5">
+        <v>6770</v>
+      </c>
+      <c r="D5">
+        <v>4372</v>
+      </c>
+      <c r="G5">
+        <v>2398</v>
+      </c>
+      <c r="AE5" t="str">
+        <v>POS export somsaijai-2026-08-01-to-31.json</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>04/08/2026</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Tue</v>
+      </c>
+      <c r="C6">
+        <v>6905</v>
+      </c>
+      <c r="D6">
+        <v>5425</v>
+      </c>
+      <c r="G6">
+        <v>1480</v>
+      </c>
+      <c r="AE6" t="str">
+        <v>POS export somsaijai-2026-08-01-to-31.json</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>05/08/2026</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Wed</v>
+      </c>
+      <c r="C7">
+        <v>6979</v>
+      </c>
+      <c r="D7">
+        <v>5050</v>
+      </c>
+      <c r="G7">
+        <v>1929</v>
+      </c>
+      <c r="AE7" t="str">
+        <v>POS export somsaijai-2026-08-01-to-31.json</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>06/08/2026</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Thu</v>
+      </c>
+      <c r="C8">
+        <v>8801</v>
+      </c>
+      <c r="D8">
+        <v>6212</v>
+      </c>
+      <c r="G8">
+        <v>2589</v>
+      </c>
+      <c r="AE8" t="str">
+        <v>POS export somsaijai-2026-08-01-to-31.json</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>07/08/2026</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Fri</v>
+      </c>
+      <c r="C9">
+        <v>9681</v>
+      </c>
+      <c r="D9">
+        <v>6741</v>
+      </c>
+      <c r="G9">
+        <v>2940</v>
+      </c>
+      <c r="AE9" t="str">
+        <v>POS export somsaijai-2026-08-01-to-31.json</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>08/08/2026</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Sat</v>
+      </c>
+      <c r="C10">
+        <v>8362</v>
+      </c>
+      <c r="D10">
+        <v>5697</v>
+      </c>
+      <c r="G10">
+        <v>2665</v>
+      </c>
+      <c r="AE10" t="str">
+        <v>POS export somsaijai-2026-08-01-to-31.json</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>09/08/2026</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Sun</v>
+      </c>
+      <c r="C11">
+        <v>8425</v>
+      </c>
+      <c r="D11">
+        <v>6261</v>
+      </c>
+      <c r="G11">
+        <v>2164</v>
+      </c>
+      <c r="AE11" t="str">
+        <v>POS export somsaijai-2026-08-01-to-31.json</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>10/08/2026</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Mon</v>
+      </c>
+      <c r="C12">
+        <v>8971</v>
+      </c>
+      <c r="D12">
+        <v>6655</v>
+      </c>
+      <c r="G12">
+        <v>2316</v>
+      </c>
+      <c r="AE12" t="str">
+        <v>POS export somsaijai-2026-08-01-to-31.json</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>11/08/2026</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Tue</v>
+      </c>
+      <c r="C13">
+        <v>7803</v>
+      </c>
+      <c r="D13">
+        <v>6345</v>
+      </c>
+      <c r="G13">
+        <v>1458</v>
+      </c>
+      <c r="AE13" t="str">
+        <v>POS export somsaijai-2026-08-01-to-31.json</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>12/08/2026</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Wed</v>
+      </c>
+      <c r="C14">
+        <v>7970</v>
+      </c>
+      <c r="D14">
+        <v>6741</v>
+      </c>
+      <c r="G14">
+        <v>1229</v>
+      </c>
+      <c r="AE14" t="str">
+        <v>POS export somsaijai-2026-08-01-to-31.json</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>13/08/2026</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Thu</v>
+      </c>
+      <c r="C15">
+        <v>8184</v>
+      </c>
+      <c r="D15">
+        <v>6527</v>
+      </c>
+      <c r="G15">
+        <v>1657</v>
+      </c>
+      <c r="AE15" t="str">
+        <v>POS export somsaijai-2026-08-01-to-31.json</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>14/08/2026</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Fri</v>
+      </c>
+      <c r="C16">
+        <v>10304</v>
+      </c>
+      <c r="D16">
+        <v>7184</v>
+      </c>
+      <c r="G16">
+        <v>3120</v>
+      </c>
+      <c r="AE16" t="str">
+        <v>POS export somsaijai-2026-08-01-to-31.json</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>15/08/2026</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Sat</v>
+      </c>
+      <c r="C17">
+        <v>8770</v>
+      </c>
+      <c r="D17">
+        <v>7015</v>
+      </c>
+      <c r="G17">
+        <v>1755</v>
+      </c>
+      <c r="AE17" t="str">
+        <v>POS export somsaijai-2026-08-01-to-31.json</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>16/08/2026</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Sun</v>
+      </c>
+      <c r="C18">
+        <v>10551</v>
+      </c>
+      <c r="D18">
+        <v>9662</v>
+      </c>
+      <c r="G18">
+        <v>889</v>
+      </c>
+      <c r="AE18" t="str">
+        <v>POS export somsaijai-2026-08-01-to-31.json</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>17/08/2026</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Mon</v>
+      </c>
+      <c r="C19">
+        <v>9334</v>
+      </c>
+      <c r="D19">
+        <v>7606</v>
+      </c>
+      <c r="G19">
+        <v>1728</v>
+      </c>
+      <c r="AE19" t="str">
+        <v>POS export somsaijai-2026-08-01-to-31.json</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Tue</v>
+      </c>
+      <c r="C20">
+        <v>11114</v>
+      </c>
+      <c r="D20">
+        <v>8248</v>
+      </c>
+      <c r="G20">
+        <v>2866</v>
+      </c>
+      <c r="AE20" t="str">
+        <v>POS export somsaijai-2026-08-01-to-31.json</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>19/08/2026</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Wed</v>
+      </c>
+      <c r="C21">
+        <v>7255</v>
+      </c>
+      <c r="D21">
+        <v>5236</v>
+      </c>
+      <c r="G21">
+        <v>2019</v>
+      </c>
+      <c r="AE21" t="str">
+        <v>POS export somsaijai-2026-08-01-to-31.json</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>20/08/2026</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Thu</v>
+      </c>
+      <c r="C22">
+        <v>9164</v>
+      </c>
+      <c r="D22">
+        <v>7228</v>
+      </c>
+      <c r="G22">
+        <v>1936</v>
+      </c>
+      <c r="AE22" t="str">
+        <v>POS export somsaijai-2026-08-01-to-31.json</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>21/08/2026</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Fri</v>
+      </c>
+      <c r="C23">
+        <v>10251</v>
+      </c>
+      <c r="D23">
+        <v>6996</v>
+      </c>
+      <c r="G23">
+        <v>3255</v>
+      </c>
+      <c r="AE23" t="str">
+        <v>POS export somsaijai-2026-08-01-to-31.json</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>22/08/2026</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Sat</v>
+      </c>
+      <c r="C24">
+        <v>5640</v>
+      </c>
+      <c r="D24">
+        <v>4843</v>
+      </c>
+      <c r="G24">
+        <v>797</v>
+      </c>
+      <c r="AE24" t="str">
+        <v>POS export somsaijai-2026-08-01-to-31.json</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>23/08/2026</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Sun</v>
+      </c>
+      <c r="C25">
+        <v>3963</v>
+      </c>
+      <c r="D25">
+        <v>2907</v>
+      </c>
+      <c r="G25">
+        <v>1056</v>
+      </c>
+      <c r="AE25" t="str">
+        <v>POS export somsaijai-2026-08-01-to-31.json</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>24/08/2026</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Mon</v>
+      </c>
+      <c r="C26">
+        <v>7754</v>
+      </c>
+      <c r="D26">
+        <v>6191</v>
+      </c>
+      <c r="G26">
+        <v>1563</v>
+      </c>
+      <c r="AE26" t="str">
+        <v>POS export somsaijai-2026-08-01-to-31.json</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>25/08/2026</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Tue</v>
+      </c>
+      <c r="C27">
+        <v>5490</v>
+      </c>
+      <c r="D27">
+        <v>4081</v>
+      </c>
+      <c r="G27">
+        <v>1409</v>
+      </c>
+      <c r="AE27" t="str">
+        <v>POS export somsaijai-2026-08-01-to-31.json</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>26/08/2026</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Wed</v>
+      </c>
+      <c r="C28">
+        <v>7181</v>
+      </c>
+      <c r="D28">
+        <v>5338</v>
+      </c>
+      <c r="G28">
+        <v>1843</v>
+      </c>
+      <c r="AE28" t="str">
+        <v>POS export somsaijai-2026-08-01-to-31.json</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>27/08/2026</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Thu</v>
+      </c>
+      <c r="C29">
+        <v>3969</v>
+      </c>
+      <c r="D29">
+        <v>2790</v>
+      </c>
+      <c r="G29">
+        <v>1179</v>
+      </c>
+      <c r="AE29" t="str">
+        <v>POS export somsaijai-2026-08-01-to-31.json</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>28/08/2026</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Fri</v>
+      </c>
+      <c r="C30">
+        <v>5675</v>
+      </c>
+      <c r="D30">
+        <v>4485</v>
+      </c>
+      <c r="G30">
+        <v>1190</v>
+      </c>
+      <c r="AE30" t="str">
+        <v>POS export somsaijai-2026-08-01-to-31.json</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>29/08/2026</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Sat</v>
+      </c>
+      <c r="C31">
+        <v>6256</v>
+      </c>
+      <c r="D31">
+        <v>4082</v>
+      </c>
+      <c r="G31">
+        <v>2174</v>
+      </c>
+      <c r="AE31" t="str">
+        <v>POS export somsaijai-2026-08-01-to-31.json</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>30/08/2026</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Sun</v>
+      </c>
+      <c r="C32">
+        <v>5509</v>
+      </c>
+      <c r="D32">
+        <v>4626</v>
+      </c>
+      <c r="G32">
+        <v>883</v>
+      </c>
+      <c r="AE32" t="str">
+        <v>POS export somsaijai-2026-08-01-to-31.json</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>31/08/2026</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Mon</v>
+      </c>
+      <c r="C33">
+        <v>5965</v>
+      </c>
+      <c r="D33">
+        <v>4120</v>
+      </c>
+      <c r="G33">
+        <v>1845</v>
+      </c>
+      <c r="AE33" t="str">
+        <v>POS export somsaijai-2026-08-01-to-31.json</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AD2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AE33"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/3_Automation_Dashboard/SomSaiJai_Dashboard_B3_2026.xlsx
+++ b/3_Automation_Dashboard/SomSaiJai_Dashboard_B3_2026.xlsx
@@ -133,10 +133,10 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ÃÂ¯ÃÂ¼ÃÂ­ÃÂ¯ÃÂ¼ÃÂ³ ÃÂ¯ÃÂ¼ÃÂ°ÃÂ£ÃÂÃÂ´ÃÂ£ÃÂÃÂ·ÃÂ£ÃÂÃÂÃÂ£ÃÂÃÂ¯"/>
-        <a:font script="Hang" typeface="ÃÂ«ÃÂ§ÃÂÃÂ¬ÃÂÃÂ ÃÂªÃÂ³ÃÂ ÃÂ«ÃÂÃÂ"/>
-        <a:font script="Hans" typeface="ÃÂ¥ÃÂ®ÃÂÃÂ¤ÃÂ½ÃÂ"/>
-        <a:font script="Hant" typeface="ÃÂ¦ÃÂÃÂ°ÃÂ§ÃÂ´ÃÂ°ÃÂ¦ÃÂÃÂÃÂ©ÃÂ«ÃÂ"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -168,10 +168,10 @@
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ÃÂ¯ÃÂ¼ÃÂ­ÃÂ¯ÃÂ¼ÃÂ³ ÃÂ¯ÃÂ¼ÃÂ°ÃÂ£ÃÂÃÂ´ÃÂ£ÃÂÃÂ·ÃÂ£ÃÂÃÂÃÂ£ÃÂÃÂ¯"/>
-        <a:font script="Hang" typeface="ÃÂ«ÃÂ§ÃÂÃÂ¬ÃÂÃÂ ÃÂªÃÂ³ÃÂ ÃÂ«ÃÂÃÂ"/>
-        <a:font script="Hans" typeface="ÃÂ¥ÃÂ®ÃÂÃÂ¤ÃÂ½ÃÂ"/>
-        <a:font script="Hant" typeface="ÃÂ¦ÃÂÃÂ°ÃÂ§ÃÂ´ÃÂ°ÃÂ¦ÃÂÃÂÃÂ©ÃÂ«ÃÂ"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -2773,7 +2773,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F31"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3190,9 +3190,169 @@
         <v>3500</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>30/09/2026</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Sep26</v>
+      </c>
+      <c r="C24" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D24" t="str">
+        <v>Durian</v>
+      </c>
+      <c r="E24" t="str">
+        <v>ทุเรียน B3 (Slips 79, 83, 84)</v>
+      </c>
+      <c r="F24">
+        <v>9670</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>30/09/2026</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Sep26</v>
+      </c>
+      <c r="C25" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D25" t="str">
+        <v>Sticky Rice</v>
+      </c>
+      <c r="E25" t="str">
+        <v>ข้าวเหนียวมูน B3 ก.ย.</v>
+      </c>
+      <c r="F25">
+        <v>13174</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>21/09/2026</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Sep26</v>
+      </c>
+      <c r="C26" t="str">
+        <v>OPEX</v>
+      </c>
+      <c r="D26" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="E26" t="str">
+        <v>ค่าเช่า B3 เดือน Sep (Slip 48)</v>
+      </c>
+      <c r="F26">
+        <v>18780.22</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>30/09/2026</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Sep26</v>
+      </c>
+      <c r="C27" t="str">
+        <v>OPEX</v>
+      </c>
+      <c r="D27" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="E27" t="str">
+        <v>ค่าเช่า storage เดือน 9 (1/4 split B3)</v>
+      </c>
+      <c r="F27">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>30/09/2026</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Sep26</v>
+      </c>
+      <c r="C28" t="str">
+        <v>OPEX</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Utilities</v>
+      </c>
+      <c r="E28" t="str">
+        <v>ค่าไฟ B3 เดือน Aug (Slip 45)</v>
+      </c>
+      <c r="F28">
+        <v>1592.22</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>30/09/2026</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Sep26</v>
+      </c>
+      <c r="C29" t="str">
+        <v>OPEX</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Salary</v>
+      </c>
+      <c r="E29" t="str">
+        <v>เงินเดือนพนักงาน B3 ก.ย. (Arkar 15k + HtunKyaw 15k + Tae 15k)</v>
+      </c>
+      <c r="F29">
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>04/09/2026</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Sep26</v>
+      </c>
+      <c r="C30" t="str">
+        <v>OPEX</v>
+      </c>
+      <c r="D30" t="str">
+        <v>Salary</v>
+      </c>
+      <c r="E30" t="str">
+        <v>Ming manager wage Sep (1/4 of ฿20,000; Slip 47)</v>
+      </c>
+      <c r="F30">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>30/09/2026</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Sep26</v>
+      </c>
+      <c r="C31" t="str">
+        <v>OPEX</v>
+      </c>
+      <c r="D31" t="str">
+        <v>Other OPEX</v>
+      </c>
+      <c r="E31" t="str">
+        <v>ค่าขนส่ง / logistics / supplies Sep (B3 portion 45.10%)</v>
+      </c>
+      <c r="F31">
+        <v>5592.59</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F23"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F31"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -4578,108 +4738,3054 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AD2"/>
+  <dimension ref="A1:AF33"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>SomSaiJai Branch 3 (Platinum Pop) - Sep26</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
+        <v>Som Sai Jai Cold Press Bar (B3) - September 2026</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
         <v>Date</v>
       </c>
-      <c r="B2" t="str">
+      <c r="B3" t="str">
         <v>Day</v>
       </c>
-      <c r="C2" t="str">
+      <c r="C3" t="str">
         <v>Revenue (฿)</v>
       </c>
-      <c r="D2" t="str">
+      <c r="D3" t="str">
         <v>Cash (฿)</v>
       </c>
-      <c r="E2" t="str">
+      <c r="E3" t="str">
         <v>Expenses (฿)</v>
       </c>
-      <c r="F2" t="str">
+      <c r="F3" t="str">
         <v>Cash-Exp (฿)</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G3" t="str">
         <v>Scan/Transfer (฿)</v>
       </c>
-      <c r="H2" t="str">
+      <c r="H3" t="str">
         <v>Orange</v>
       </c>
-      <c r="I2" t="str">
+      <c r="I3" t="str">
         <v>Orange (100)</v>
       </c>
-      <c r="J2" t="str">
+      <c r="J3" t="str">
         <v>Watermelon</v>
       </c>
-      <c r="K2" t="str">
+      <c r="K3" t="str">
         <v>Mango</v>
       </c>
-      <c r="L2" t="str">
+      <c r="L3" t="str">
         <v>Coconut</v>
       </c>
-      <c r="M2" t="str">
+      <c r="M3" t="str">
         <v>Apple</v>
       </c>
-      <c r="N2" t="str">
+      <c r="N3" t="str">
         <v>Young Coco</v>
       </c>
-      <c r="O2" t="str">
+      <c r="O3" t="str">
         <v>Guava</v>
       </c>
-      <c r="P2" t="str">
+      <c r="P3" t="str">
         <v>Pineapple</v>
       </c>
-      <c r="Q2" t="str">
+      <c r="Q3" t="str">
         <v>Total Cups</v>
       </c>
-      <c r="R2" t="str">
+      <c r="R3" t="str">
         <v>Bot Big</v>
       </c>
-      <c r="S2" t="str">
+      <c r="S3" t="str">
         <v>Bot Small</v>
       </c>
-      <c r="T2" t="str">
+      <c r="T3" t="str">
         <v>Used Orange (basket)</v>
       </c>
-      <c r="U2" t="str">
+      <c r="U3" t="str">
         <v>Used Watermelon (pcs)</v>
       </c>
-      <c r="V2" t="str">
+      <c r="V3" t="str">
         <v>Used Mango</v>
       </c>
-      <c r="W2" t="str">
+      <c r="W3" t="str">
         <v>Used Coco (Meat)</v>
       </c>
-      <c r="X2" t="str">
+      <c r="X3" t="str">
         <v>Used Coco (Water)</v>
       </c>
-      <c r="Y2" t="str">
+      <c r="Y3" t="str">
         <v>Used Coco (Conden)</v>
       </c>
-      <c r="Z2" t="str">
+      <c r="Z3" t="str">
         <v>Used Coco (Raw)</v>
       </c>
-      <c r="AA2" t="str">
+      <c r="AA3" t="str">
         <v>Used Apple</v>
       </c>
-      <c r="AB2" t="str">
+      <c r="AB3" t="str">
         <v>Used Guava</v>
       </c>
-      <c r="AC2" t="str">
+      <c r="AC3" t="str">
         <v>Used Pineapple</v>
       </c>
-      <c r="AD2" t="str">
+      <c r="AD3" t="str">
         <v>Used Young Coco</v>
+      </c>
+      <c r="AE3" t="str">
+        <v>Bottle Revenue (฿)</v>
+      </c>
+      <c r="AF3" t="str">
+        <v>Source Note</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>01/09/2026</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Tue</v>
+      </c>
+      <c r="C4">
+        <v>6552</v>
+      </c>
+      <c r="D4">
+        <v>5169</v>
+      </c>
+      <c r="E4">
+        <v>110</v>
+      </c>
+      <c r="F4">
+        <v>5059</v>
+      </c>
+      <c r="G4">
+        <v>1383</v>
+      </c>
+      <c r="H4">
+        <v>9</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>18</v>
+      </c>
+      <c r="K4">
+        <v>6</v>
+      </c>
+      <c r="L4">
+        <v>8</v>
+      </c>
+      <c r="M4">
+        <v>3</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>9</v>
+      </c>
+      <c r="P4">
+        <v>8</v>
+      </c>
+      <c r="Q4">
+        <v>71</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>9</v>
+      </c>
+      <c r="U4">
+        <v>18</v>
+      </c>
+      <c r="V4">
+        <v>6</v>
+      </c>
+      <c r="W4">
+        <v>0</v>
+      </c>
+      <c r="X4">
+        <v>0</v>
+      </c>
+      <c r="Y4">
+        <v>0</v>
+      </c>
+      <c r="Z4">
+        <v>8</v>
+      </c>
+      <c r="AA4">
+        <v>3</v>
+      </c>
+      <c r="AB4">
+        <v>9</v>
+      </c>
+      <c r="AC4">
+        <v>8</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="str">
+        <v>LINE_ALBUM_Daily Sales Report B3(September)_261001_30.jpg</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>02/09/2026</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Wed</v>
+      </c>
+      <c r="C5">
+        <v>7620</v>
+      </c>
+      <c r="D5">
+        <v>6661</v>
+      </c>
+      <c r="E5">
+        <v>110</v>
+      </c>
+      <c r="F5">
+        <v>6551</v>
+      </c>
+      <c r="G5">
+        <v>959</v>
+      </c>
+      <c r="H5">
+        <v>15</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>19</v>
+      </c>
+      <c r="K5">
+        <v>10</v>
+      </c>
+      <c r="L5">
+        <v>11</v>
+      </c>
+      <c r="M5">
+        <v>7</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>12</v>
+      </c>
+      <c r="P5">
+        <v>9</v>
+      </c>
+      <c r="Q5">
+        <v>90</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>15</v>
+      </c>
+      <c r="U5">
+        <v>19</v>
+      </c>
+      <c r="V5">
+        <v>10</v>
+      </c>
+      <c r="W5">
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <v>0</v>
+      </c>
+      <c r="Y5">
+        <v>0</v>
+      </c>
+      <c r="Z5">
+        <v>11</v>
+      </c>
+      <c r="AA5">
+        <v>7</v>
+      </c>
+      <c r="AB5">
+        <v>12</v>
+      </c>
+      <c r="AC5">
+        <v>9</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="str">
+        <v>LINE_ALBUM_Daily Sales Report B3(September)_261001_29.jpg</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>03/09/2026</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Thu</v>
+      </c>
+      <c r="C6">
+        <v>5512</v>
+      </c>
+      <c r="D6">
+        <v>4632</v>
+      </c>
+      <c r="E6">
+        <v>110</v>
+      </c>
+      <c r="F6">
+        <v>4522</v>
+      </c>
+      <c r="G6">
+        <v>880</v>
+      </c>
+      <c r="H6">
+        <v>9</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>21</v>
+      </c>
+      <c r="K6">
+        <v>4</v>
+      </c>
+      <c r="L6">
+        <v>17</v>
+      </c>
+      <c r="M6">
+        <v>6</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>9</v>
+      </c>
+      <c r="P6">
+        <v>5</v>
+      </c>
+      <c r="Q6">
+        <v>73</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>9</v>
+      </c>
+      <c r="U6">
+        <v>21</v>
+      </c>
+      <c r="V6">
+        <v>4</v>
+      </c>
+      <c r="W6">
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <v>0</v>
+      </c>
+      <c r="Y6">
+        <v>0</v>
+      </c>
+      <c r="Z6">
+        <v>17</v>
+      </c>
+      <c r="AA6">
+        <v>6</v>
+      </c>
+      <c r="AB6">
+        <v>9</v>
+      </c>
+      <c r="AC6">
+        <v>5</v>
+      </c>
+      <c r="AD6">
+        <v>0</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="str">
+        <v>LINE_ALBUM_Daily Sales Report B3(September)_261001_27.jpg</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>04/09/2026</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Fri</v>
+      </c>
+      <c r="C7">
+        <v>5686</v>
+      </c>
+      <c r="D7">
+        <v>4981</v>
+      </c>
+      <c r="E7">
+        <v>55</v>
+      </c>
+      <c r="F7">
+        <v>4926</v>
+      </c>
+      <c r="G7">
+        <v>705</v>
+      </c>
+      <c r="H7">
+        <v>10</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>17</v>
+      </c>
+      <c r="K7">
+        <v>7</v>
+      </c>
+      <c r="L7">
+        <v>20</v>
+      </c>
+      <c r="M7">
+        <v>4</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>5</v>
+      </c>
+      <c r="P7">
+        <v>3</v>
+      </c>
+      <c r="Q7">
+        <v>71</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>10</v>
+      </c>
+      <c r="U7">
+        <v>17</v>
+      </c>
+      <c r="V7">
+        <v>7</v>
+      </c>
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <v>0</v>
+      </c>
+      <c r="Z7">
+        <v>20</v>
+      </c>
+      <c r="AA7">
+        <v>4</v>
+      </c>
+      <c r="AB7">
+        <v>5</v>
+      </c>
+      <c r="AC7">
+        <v>3</v>
+      </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="str">
+        <v>LINE_ALBUM_Daily Sales Report B3(September)_261001_28.jpg</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>05/09/2026</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Sat</v>
+      </c>
+      <c r="C8">
+        <v>7588</v>
+      </c>
+      <c r="D8">
+        <v>6139</v>
+      </c>
+      <c r="E8">
+        <v>110</v>
+      </c>
+      <c r="F8">
+        <v>6029</v>
+      </c>
+      <c r="G8">
+        <v>1449</v>
+      </c>
+      <c r="H8">
+        <v>10</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>8</v>
+      </c>
+      <c r="K8">
+        <v>11</v>
+      </c>
+      <c r="L8">
+        <v>18</v>
+      </c>
+      <c r="M8">
+        <v>4</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>5</v>
+      </c>
+      <c r="P8">
+        <v>11</v>
+      </c>
+      <c r="Q8">
+        <v>76</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>10</v>
+      </c>
+      <c r="U8">
+        <v>8</v>
+      </c>
+      <c r="V8">
+        <v>11</v>
+      </c>
+      <c r="W8">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>0</v>
+      </c>
+      <c r="Y8">
+        <v>0</v>
+      </c>
+      <c r="Z8">
+        <v>18</v>
+      </c>
+      <c r="AA8">
+        <v>4</v>
+      </c>
+      <c r="AB8">
+        <v>5</v>
+      </c>
+      <c r="AC8">
+        <v>11</v>
+      </c>
+      <c r="AD8">
+        <v>0</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="str">
+        <v>LINE_ALBUM_Daily Sales Report B3(September)_261001_26.jpg</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>06/09/2026</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Sun</v>
+      </c>
+      <c r="C9">
+        <v>8400</v>
+      </c>
+      <c r="D9">
+        <v>5664</v>
+      </c>
+      <c r="E9">
+        <v>110</v>
+      </c>
+      <c r="F9">
+        <v>5554</v>
+      </c>
+      <c r="G9">
+        <v>2736</v>
+      </c>
+      <c r="H9">
+        <v>15</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>24</v>
+      </c>
+      <c r="K9">
+        <v>3</v>
+      </c>
+      <c r="L9">
+        <v>22</v>
+      </c>
+      <c r="M9">
+        <v>7</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>9</v>
+      </c>
+      <c r="P9">
+        <v>7</v>
+      </c>
+      <c r="Q9">
+        <v>103</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>15</v>
+      </c>
+      <c r="U9">
+        <v>24</v>
+      </c>
+      <c r="V9">
+        <v>3</v>
+      </c>
+      <c r="W9">
+        <v>0</v>
+      </c>
+      <c r="X9">
+        <v>0</v>
+      </c>
+      <c r="Y9">
+        <v>0</v>
+      </c>
+      <c r="Z9">
+        <v>22</v>
+      </c>
+      <c r="AA9">
+        <v>7</v>
+      </c>
+      <c r="AB9">
+        <v>9</v>
+      </c>
+      <c r="AC9">
+        <v>7</v>
+      </c>
+      <c r="AD9">
+        <v>0</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="str">
+        <v>LINE_ALBUM_Daily Sales Report B3(September)_261001_25.jpg</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>07/09/2026</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Mon</v>
+      </c>
+      <c r="C10">
+        <v>4493</v>
+      </c>
+      <c r="D10">
+        <v>3175</v>
+      </c>
+      <c r="E10">
+        <v>110</v>
+      </c>
+      <c r="F10">
+        <v>3065</v>
+      </c>
+      <c r="G10">
+        <v>1318</v>
+      </c>
+      <c r="H10">
+        <v>5</v>
+      </c>
+      <c r="I10">
+        <v>2</v>
+      </c>
+      <c r="J10">
+        <v>8</v>
+      </c>
+      <c r="K10">
+        <v>6</v>
+      </c>
+      <c r="L10">
+        <v>14</v>
+      </c>
+      <c r="M10">
+        <v>4</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>2</v>
+      </c>
+      <c r="P10">
+        <v>4</v>
+      </c>
+      <c r="Q10">
+        <v>51</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>5</v>
+      </c>
+      <c r="U10">
+        <v>8</v>
+      </c>
+      <c r="V10">
+        <v>6</v>
+      </c>
+      <c r="W10">
+        <v>0</v>
+      </c>
+      <c r="X10">
+        <v>0</v>
+      </c>
+      <c r="Y10">
+        <v>0</v>
+      </c>
+      <c r="Z10">
+        <v>14</v>
+      </c>
+      <c r="AA10">
+        <v>4</v>
+      </c>
+      <c r="AB10">
+        <v>2</v>
+      </c>
+      <c r="AC10">
+        <v>4</v>
+      </c>
+      <c r="AD10">
+        <v>0</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="str">
+        <v>LINE_ALBUM_Daily Sales Report B3(September)_261001_24.jpg</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>08/09/2026</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Tue</v>
+      </c>
+      <c r="C11">
+        <v>5283</v>
+      </c>
+      <c r="D11">
+        <v>4066</v>
+      </c>
+      <c r="E11">
+        <v>110</v>
+      </c>
+      <c r="F11">
+        <v>3956</v>
+      </c>
+      <c r="G11">
+        <v>1217</v>
+      </c>
+      <c r="H11">
+        <v>7</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+      <c r="J11">
+        <v>13</v>
+      </c>
+      <c r="K11">
+        <v>9</v>
+      </c>
+      <c r="L11">
+        <v>12</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>5</v>
+      </c>
+      <c r="P11">
+        <v>6</v>
+      </c>
+      <c r="Q11">
+        <v>57</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>7</v>
+      </c>
+      <c r="U11">
+        <v>13</v>
+      </c>
+      <c r="V11">
+        <v>9</v>
+      </c>
+      <c r="W11">
+        <v>0</v>
+      </c>
+      <c r="X11">
+        <v>0</v>
+      </c>
+      <c r="Y11">
+        <v>0</v>
+      </c>
+      <c r="Z11">
+        <v>12</v>
+      </c>
+      <c r="AA11">
+        <v>0</v>
+      </c>
+      <c r="AB11">
+        <v>5</v>
+      </c>
+      <c r="AC11">
+        <v>6</v>
+      </c>
+      <c r="AD11">
+        <v>0</v>
+      </c>
+      <c r="AE11">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="str">
+        <v>LINE_ALBUM_Daily Sales Report B3(September)_261001_23.jpg</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>09/09/2026</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Wed</v>
+      </c>
+      <c r="C12">
+        <v>6167</v>
+      </c>
+      <c r="D12">
+        <v>5137</v>
+      </c>
+      <c r="E12">
+        <v>55</v>
+      </c>
+      <c r="F12">
+        <v>5082</v>
+      </c>
+      <c r="G12">
+        <v>1030</v>
+      </c>
+      <c r="H12">
+        <v>15</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+      <c r="J12">
+        <v>17</v>
+      </c>
+      <c r="K12">
+        <v>16</v>
+      </c>
+      <c r="L12">
+        <v>12</v>
+      </c>
+      <c r="M12">
+        <v>2</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>3</v>
+      </c>
+      <c r="P12">
+        <v>4</v>
+      </c>
+      <c r="Q12">
+        <v>73</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>15</v>
+      </c>
+      <c r="U12">
+        <v>17</v>
+      </c>
+      <c r="V12">
+        <v>16</v>
+      </c>
+      <c r="W12">
+        <v>0</v>
+      </c>
+      <c r="X12">
+        <v>0</v>
+      </c>
+      <c r="Y12">
+        <v>0</v>
+      </c>
+      <c r="Z12">
+        <v>12</v>
+      </c>
+      <c r="AA12">
+        <v>2</v>
+      </c>
+      <c r="AB12">
+        <v>3</v>
+      </c>
+      <c r="AC12">
+        <v>4</v>
+      </c>
+      <c r="AD12">
+        <v>0</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="str">
+        <v>LINE_ALBUM_Daily Sales Report B3(September)_261001_22.jpg</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>10/09/2026</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Thu</v>
+      </c>
+      <c r="C13">
+        <v>6513</v>
+      </c>
+      <c r="D13">
+        <v>5137</v>
+      </c>
+      <c r="E13">
+        <v>55</v>
+      </c>
+      <c r="F13">
+        <v>5082</v>
+      </c>
+      <c r="G13">
+        <v>1376</v>
+      </c>
+      <c r="H13">
+        <v>6</v>
+      </c>
+      <c r="I13">
+        <v>1</v>
+      </c>
+      <c r="J13">
+        <v>15</v>
+      </c>
+      <c r="K13">
+        <v>10</v>
+      </c>
+      <c r="L13">
+        <v>18</v>
+      </c>
+      <c r="M13">
+        <v>2</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>8</v>
+      </c>
+      <c r="P13">
+        <v>7</v>
+      </c>
+      <c r="Q13">
+        <v>78</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>6</v>
+      </c>
+      <c r="U13">
+        <v>15</v>
+      </c>
+      <c r="V13">
+        <v>10</v>
+      </c>
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>0</v>
+      </c>
+      <c r="Y13">
+        <v>0</v>
+      </c>
+      <c r="Z13">
+        <v>18</v>
+      </c>
+      <c r="AA13">
+        <v>2</v>
+      </c>
+      <c r="AB13">
+        <v>8</v>
+      </c>
+      <c r="AC13">
+        <v>7</v>
+      </c>
+      <c r="AD13">
+        <v>0</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="str">
+        <v>LINE_ALBUM_Daily Sales Report B3(September)_261001_21.jpg</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>11/09/2026</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Fri</v>
+      </c>
+      <c r="C14">
+        <v>6644</v>
+      </c>
+      <c r="D14">
+        <v>5676</v>
+      </c>
+      <c r="E14">
+        <v>110</v>
+      </c>
+      <c r="F14">
+        <v>5566</v>
+      </c>
+      <c r="G14">
+        <v>968</v>
+      </c>
+      <c r="H14">
+        <v>7</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>21</v>
+      </c>
+      <c r="K14">
+        <v>12</v>
+      </c>
+      <c r="L14">
+        <v>12</v>
+      </c>
+      <c r="M14">
+        <v>5</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>5</v>
+      </c>
+      <c r="P14">
+        <v>6</v>
+      </c>
+      <c r="Q14">
+        <v>74</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>7</v>
+      </c>
+      <c r="U14">
+        <v>21</v>
+      </c>
+      <c r="V14">
+        <v>12</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>0</v>
+      </c>
+      <c r="Y14">
+        <v>0</v>
+      </c>
+      <c r="Z14">
+        <v>12</v>
+      </c>
+      <c r="AA14">
+        <v>5</v>
+      </c>
+      <c r="AB14">
+        <v>5</v>
+      </c>
+      <c r="AC14">
+        <v>6</v>
+      </c>
+      <c r="AD14">
+        <v>0</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="str">
+        <v>LINE_ALBUM_Daily Sales Report B3(September)_261001_20.jpg</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>12/09/2026</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Sat</v>
+      </c>
+      <c r="C15">
+        <v>5409</v>
+      </c>
+      <c r="D15">
+        <v>4610</v>
+      </c>
+      <c r="E15">
+        <v>55</v>
+      </c>
+      <c r="F15">
+        <v>4555</v>
+      </c>
+      <c r="G15">
+        <v>799</v>
+      </c>
+      <c r="H15">
+        <v>12</v>
+      </c>
+      <c r="I15">
+        <v>2</v>
+      </c>
+      <c r="J15">
+        <v>10</v>
+      </c>
+      <c r="K15">
+        <v>7</v>
+      </c>
+      <c r="L15">
+        <v>9</v>
+      </c>
+      <c r="M15">
+        <v>1</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>3</v>
+      </c>
+      <c r="P15">
+        <v>2</v>
+      </c>
+      <c r="Q15">
+        <v>51</v>
+      </c>
+      <c r="R15">
+        <v>0</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <v>12</v>
+      </c>
+      <c r="U15">
+        <v>10</v>
+      </c>
+      <c r="V15">
+        <v>7</v>
+      </c>
+      <c r="W15">
+        <v>0</v>
+      </c>
+      <c r="X15">
+        <v>0</v>
+      </c>
+      <c r="Y15">
+        <v>0</v>
+      </c>
+      <c r="Z15">
+        <v>9</v>
+      </c>
+      <c r="AA15">
+        <v>1</v>
+      </c>
+      <c r="AB15">
+        <v>3</v>
+      </c>
+      <c r="AC15">
+        <v>2</v>
+      </c>
+      <c r="AD15">
+        <v>0</v>
+      </c>
+      <c r="AE15">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="str">
+        <v>LINE_ALBUM_Daily Sales Report B3(September)_261001_19.jpg</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>13/09/2026</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Sun</v>
+      </c>
+      <c r="C16">
+        <v>4216</v>
+      </c>
+      <c r="D16">
+        <v>2869</v>
+      </c>
+      <c r="E16">
+        <v>110</v>
+      </c>
+      <c r="F16">
+        <v>2759</v>
+      </c>
+      <c r="G16">
+        <v>1347</v>
+      </c>
+      <c r="H16">
+        <v>9</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>17</v>
+      </c>
+      <c r="K16">
+        <v>2</v>
+      </c>
+      <c r="L16">
+        <v>7</v>
+      </c>
+      <c r="M16">
+        <v>5</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>1</v>
+      </c>
+      <c r="P16">
+        <v>5</v>
+      </c>
+      <c r="Q16">
+        <v>52</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>9</v>
+      </c>
+      <c r="U16">
+        <v>17</v>
+      </c>
+      <c r="V16">
+        <v>2</v>
+      </c>
+      <c r="W16">
+        <v>0</v>
+      </c>
+      <c r="X16">
+        <v>0</v>
+      </c>
+      <c r="Y16">
+        <v>0</v>
+      </c>
+      <c r="Z16">
+        <v>7</v>
+      </c>
+      <c r="AA16">
+        <v>5</v>
+      </c>
+      <c r="AB16">
+        <v>1</v>
+      </c>
+      <c r="AC16">
+        <v>5</v>
+      </c>
+      <c r="AD16">
+        <v>0</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="str">
+        <v>LINE_ALBUM_Daily Sales Report B3(September)_261001_18.jpg</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>14/09/2026</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Mon</v>
+      </c>
+      <c r="C17">
+        <v>4582</v>
+      </c>
+      <c r="D17">
+        <v>3739</v>
+      </c>
+      <c r="E17">
+        <v>175</v>
+      </c>
+      <c r="F17">
+        <v>3564</v>
+      </c>
+      <c r="G17">
+        <v>843</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>1</v>
+      </c>
+      <c r="J17">
+        <v>8</v>
+      </c>
+      <c r="K17">
+        <v>7</v>
+      </c>
+      <c r="L17">
+        <v>11</v>
+      </c>
+      <c r="M17">
+        <v>6</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>5</v>
+      </c>
+      <c r="P17">
+        <v>4</v>
+      </c>
+      <c r="Q17">
+        <v>51</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
+      <c r="U17">
+        <v>8</v>
+      </c>
+      <c r="V17">
+        <v>7</v>
+      </c>
+      <c r="W17">
+        <v>0</v>
+      </c>
+      <c r="X17">
+        <v>0</v>
+      </c>
+      <c r="Y17">
+        <v>0</v>
+      </c>
+      <c r="Z17">
+        <v>11</v>
+      </c>
+      <c r="AA17">
+        <v>6</v>
+      </c>
+      <c r="AB17">
+        <v>5</v>
+      </c>
+      <c r="AC17">
+        <v>4</v>
+      </c>
+      <c r="AD17">
+        <v>0</v>
+      </c>
+      <c r="AE17">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="str">
+        <v>LINE_ALBUM_Daily Sales Report B3(September)_261001_17.jpg</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>15/09/2026</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Tue</v>
+      </c>
+      <c r="C18">
+        <v>3932</v>
+      </c>
+      <c r="D18">
+        <v>3273</v>
+      </c>
+      <c r="E18">
+        <v>55</v>
+      </c>
+      <c r="F18">
+        <v>3218</v>
+      </c>
+      <c r="G18">
+        <v>659</v>
+      </c>
+      <c r="H18">
+        <v>8</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>15</v>
+      </c>
+      <c r="K18">
+        <v>5</v>
+      </c>
+      <c r="L18">
+        <v>5</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18">
+        <v>5</v>
+      </c>
+      <c r="P18">
+        <v>4</v>
+      </c>
+      <c r="Q18">
+        <v>46</v>
+      </c>
+      <c r="R18">
+        <v>0</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <v>8</v>
+      </c>
+      <c r="U18">
+        <v>15</v>
+      </c>
+      <c r="V18">
+        <v>5</v>
+      </c>
+      <c r="W18">
+        <v>0</v>
+      </c>
+      <c r="X18">
+        <v>0</v>
+      </c>
+      <c r="Y18">
+        <v>0</v>
+      </c>
+      <c r="Z18">
+        <v>5</v>
+      </c>
+      <c r="AA18">
+        <v>0</v>
+      </c>
+      <c r="AB18">
+        <v>5</v>
+      </c>
+      <c r="AC18">
+        <v>4</v>
+      </c>
+      <c r="AD18">
+        <v>0</v>
+      </c>
+      <c r="AE18">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="str">
+        <v>LINE_ALBUM_Daily Sales Report B3(September)_261001_16.jpg</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>16/09/2026</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Wed</v>
+      </c>
+      <c r="C19">
+        <v>4602</v>
+      </c>
+      <c r="D19">
+        <v>3729</v>
+      </c>
+      <c r="E19">
+        <v>55</v>
+      </c>
+      <c r="F19">
+        <v>3674</v>
+      </c>
+      <c r="G19">
+        <v>873</v>
+      </c>
+      <c r="H19">
+        <v>6</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>14</v>
+      </c>
+      <c r="K19">
+        <v>2</v>
+      </c>
+      <c r="L19">
+        <v>21</v>
+      </c>
+      <c r="M19">
+        <v>3</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>6</v>
+      </c>
+      <c r="P19">
+        <v>6</v>
+      </c>
+      <c r="Q19">
+        <v>61</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>6</v>
+      </c>
+      <c r="U19">
+        <v>14</v>
+      </c>
+      <c r="V19">
+        <v>2</v>
+      </c>
+      <c r="W19">
+        <v>0</v>
+      </c>
+      <c r="X19">
+        <v>0</v>
+      </c>
+      <c r="Y19">
+        <v>0</v>
+      </c>
+      <c r="Z19">
+        <v>21</v>
+      </c>
+      <c r="AA19">
+        <v>3</v>
+      </c>
+      <c r="AB19">
+        <v>6</v>
+      </c>
+      <c r="AC19">
+        <v>6</v>
+      </c>
+      <c r="AD19">
+        <v>0</v>
+      </c>
+      <c r="AE19">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="str">
+        <v>LINE_ALBUM_Daily Sales Report B3(September)_261001_15.jpg</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>17/09/2026</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Thu</v>
+      </c>
+      <c r="C20">
+        <v>4797</v>
+      </c>
+      <c r="D20">
+        <v>3767</v>
+      </c>
+      <c r="E20">
+        <v>315</v>
+      </c>
+      <c r="F20">
+        <v>3452</v>
+      </c>
+      <c r="G20">
+        <v>880</v>
+      </c>
+      <c r="H20">
+        <v>4</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>16</v>
+      </c>
+      <c r="K20">
+        <v>8</v>
+      </c>
+      <c r="L20">
+        <v>15</v>
+      </c>
+      <c r="M20">
+        <v>5</v>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20">
+        <v>2</v>
+      </c>
+      <c r="P20">
+        <v>3</v>
+      </c>
+      <c r="Q20">
+        <v>60</v>
+      </c>
+      <c r="R20">
+        <v>0</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <v>4</v>
+      </c>
+      <c r="U20">
+        <v>16</v>
+      </c>
+      <c r="V20">
+        <v>8</v>
+      </c>
+      <c r="W20">
+        <v>0</v>
+      </c>
+      <c r="X20">
+        <v>0</v>
+      </c>
+      <c r="Y20">
+        <v>0</v>
+      </c>
+      <c r="Z20">
+        <v>15</v>
+      </c>
+      <c r="AA20">
+        <v>5</v>
+      </c>
+      <c r="AB20">
+        <v>2</v>
+      </c>
+      <c r="AC20">
+        <v>3</v>
+      </c>
+      <c r="AD20">
+        <v>0</v>
+      </c>
+      <c r="AE20">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="str">
+        <v>LINE_ALBUM_Daily Sales Report B3(September)_261001_14.jpg</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>18/09/2026</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Fri</v>
+      </c>
+      <c r="C21">
+        <v>3723</v>
+      </c>
+      <c r="D21">
+        <v>3288</v>
+      </c>
+      <c r="E21">
+        <v>55</v>
+      </c>
+      <c r="F21">
+        <v>3233</v>
+      </c>
+      <c r="G21">
+        <v>435</v>
+      </c>
+      <c r="H21">
+        <v>9</v>
+      </c>
+      <c r="I21">
+        <v>2</v>
+      </c>
+      <c r="J21">
+        <v>15</v>
+      </c>
+      <c r="K21">
+        <v>2</v>
+      </c>
+      <c r="L21">
+        <v>13</v>
+      </c>
+      <c r="M21">
+        <v>2</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <v>3</v>
+      </c>
+      <c r="P21">
+        <v>4</v>
+      </c>
+      <c r="Q21">
+        <v>51</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <v>9</v>
+      </c>
+      <c r="U21">
+        <v>15</v>
+      </c>
+      <c r="V21">
+        <v>2</v>
+      </c>
+      <c r="W21">
+        <v>0</v>
+      </c>
+      <c r="X21">
+        <v>0</v>
+      </c>
+      <c r="Y21">
+        <v>0</v>
+      </c>
+      <c r="Z21">
+        <v>13</v>
+      </c>
+      <c r="AA21">
+        <v>2</v>
+      </c>
+      <c r="AB21">
+        <v>3</v>
+      </c>
+      <c r="AC21">
+        <v>4</v>
+      </c>
+      <c r="AD21">
+        <v>0</v>
+      </c>
+      <c r="AE21">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="str">
+        <v>LINE_ALBUM_Daily Sales Report B3(September)_261001_13.jpg</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>19/09/2026</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Sat</v>
+      </c>
+      <c r="C22">
+        <v>6138</v>
+      </c>
+      <c r="D22">
+        <v>4982</v>
+      </c>
+      <c r="E22">
+        <v>55</v>
+      </c>
+      <c r="F22">
+        <v>4927</v>
+      </c>
+      <c r="G22">
+        <v>1156</v>
+      </c>
+      <c r="H22">
+        <v>7</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>24</v>
+      </c>
+      <c r="K22">
+        <v>4</v>
+      </c>
+      <c r="L22">
+        <v>10</v>
+      </c>
+      <c r="M22">
+        <v>4</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <v>4</v>
+      </c>
+      <c r="P22">
+        <v>6</v>
+      </c>
+      <c r="Q22">
+        <v>69</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>7</v>
+      </c>
+      <c r="U22">
+        <v>24</v>
+      </c>
+      <c r="V22">
+        <v>4</v>
+      </c>
+      <c r="W22">
+        <v>0</v>
+      </c>
+      <c r="X22">
+        <v>0</v>
+      </c>
+      <c r="Y22">
+        <v>0</v>
+      </c>
+      <c r="Z22">
+        <v>10</v>
+      </c>
+      <c r="AA22">
+        <v>4</v>
+      </c>
+      <c r="AB22">
+        <v>4</v>
+      </c>
+      <c r="AC22">
+        <v>6</v>
+      </c>
+      <c r="AD22">
+        <v>0</v>
+      </c>
+      <c r="AE22">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="str">
+        <v>LINE_ALBUM_Daily Sales Report B3(September)_261001_12.jpg</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>20/09/2026</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Sun</v>
+      </c>
+      <c r="C23">
+        <v>4510</v>
+      </c>
+      <c r="D23">
+        <v>3361</v>
+      </c>
+      <c r="E23">
+        <v>110</v>
+      </c>
+      <c r="F23">
+        <v>3251</v>
+      </c>
+      <c r="G23">
+        <v>1149</v>
+      </c>
+      <c r="H23">
+        <v>5</v>
+      </c>
+      <c r="I23">
+        <v>2</v>
+      </c>
+      <c r="J23">
+        <v>20</v>
+      </c>
+      <c r="K23">
+        <v>8</v>
+      </c>
+      <c r="L23">
+        <v>8</v>
+      </c>
+      <c r="M23">
+        <v>2</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <v>3</v>
+      </c>
+      <c r="P23">
+        <v>6</v>
+      </c>
+      <c r="Q23">
+        <v>57</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>5</v>
+      </c>
+      <c r="U23">
+        <v>20</v>
+      </c>
+      <c r="V23">
+        <v>8</v>
+      </c>
+      <c r="W23">
+        <v>0</v>
+      </c>
+      <c r="X23">
+        <v>0</v>
+      </c>
+      <c r="Y23">
+        <v>0</v>
+      </c>
+      <c r="Z23">
+        <v>8</v>
+      </c>
+      <c r="AA23">
+        <v>2</v>
+      </c>
+      <c r="AB23">
+        <v>3</v>
+      </c>
+      <c r="AC23">
+        <v>6</v>
+      </c>
+      <c r="AD23">
+        <v>0</v>
+      </c>
+      <c r="AE23">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="str">
+        <v>LINE_ALBUM_Daily Sales Report B3(September)_261001_11.jpg</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>21/09/2026</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Mon</v>
+      </c>
+      <c r="C24">
+        <v>5010</v>
+      </c>
+      <c r="D24">
+        <v>4202</v>
+      </c>
+      <c r="E24">
+        <v>55</v>
+      </c>
+      <c r="F24">
+        <v>4147</v>
+      </c>
+      <c r="G24">
+        <v>808</v>
+      </c>
+      <c r="H24">
+        <v>9</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>10</v>
+      </c>
+      <c r="K24">
+        <v>8</v>
+      </c>
+      <c r="L24">
+        <v>14</v>
+      </c>
+      <c r="M24">
+        <v>4</v>
+      </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24">
+        <v>7</v>
+      </c>
+      <c r="P24">
+        <v>7</v>
+      </c>
+      <c r="Q24">
+        <v>62</v>
+      </c>
+      <c r="R24">
+        <v>0</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+      <c r="T24">
+        <v>9</v>
+      </c>
+      <c r="U24">
+        <v>10</v>
+      </c>
+      <c r="V24">
+        <v>8</v>
+      </c>
+      <c r="W24">
+        <v>0</v>
+      </c>
+      <c r="X24">
+        <v>0</v>
+      </c>
+      <c r="Y24">
+        <v>0</v>
+      </c>
+      <c r="Z24">
+        <v>14</v>
+      </c>
+      <c r="AA24">
+        <v>4</v>
+      </c>
+      <c r="AB24">
+        <v>7</v>
+      </c>
+      <c r="AC24">
+        <v>7</v>
+      </c>
+      <c r="AD24">
+        <v>0</v>
+      </c>
+      <c r="AE24">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="str">
+        <v>LINE_ALBUM_Daily Sales Report B3(September)_261001_10.jpg</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>22/09/2026</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Tue</v>
+      </c>
+      <c r="C25">
+        <v>3772</v>
+      </c>
+      <c r="D25">
+        <v>2706</v>
+      </c>
+      <c r="E25">
+        <v>358</v>
+      </c>
+      <c r="F25">
+        <v>2348</v>
+      </c>
+      <c r="G25">
+        <v>1066</v>
+      </c>
+      <c r="H25">
+        <v>7</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>14</v>
+      </c>
+      <c r="K25">
+        <v>5</v>
+      </c>
+      <c r="L25">
+        <v>8</v>
+      </c>
+      <c r="M25">
+        <v>5</v>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25">
+        <v>2</v>
+      </c>
+      <c r="P25">
+        <v>1</v>
+      </c>
+      <c r="Q25">
+        <v>48</v>
+      </c>
+      <c r="R25">
+        <v>0</v>
+      </c>
+      <c r="S25">
+        <v>0</v>
+      </c>
+      <c r="T25">
+        <v>7</v>
+      </c>
+      <c r="U25">
+        <v>14</v>
+      </c>
+      <c r="V25">
+        <v>5</v>
+      </c>
+      <c r="W25">
+        <v>0</v>
+      </c>
+      <c r="X25">
+        <v>0</v>
+      </c>
+      <c r="Y25">
+        <v>0</v>
+      </c>
+      <c r="Z25">
+        <v>8</v>
+      </c>
+      <c r="AA25">
+        <v>5</v>
+      </c>
+      <c r="AB25">
+        <v>2</v>
+      </c>
+      <c r="AC25">
+        <v>1</v>
+      </c>
+      <c r="AD25">
+        <v>0</v>
+      </c>
+      <c r="AE25">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="str">
+        <v>LINE_ALBUM_Daily Sales Report B3(September)_261001_9.jpg</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>23/09/2026</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Wed</v>
+      </c>
+      <c r="C26">
+        <v>4473</v>
+      </c>
+      <c r="D26">
+        <v>3390</v>
+      </c>
+      <c r="E26">
+        <v>55</v>
+      </c>
+      <c r="F26">
+        <v>3335</v>
+      </c>
+      <c r="G26">
+        <v>1083</v>
+      </c>
+      <c r="H26">
+        <v>13</v>
+      </c>
+      <c r="I26">
+        <v>1</v>
+      </c>
+      <c r="J26">
+        <v>10</v>
+      </c>
+      <c r="K26">
+        <v>4</v>
+      </c>
+      <c r="L26">
+        <v>11</v>
+      </c>
+      <c r="M26">
+        <v>4</v>
+      </c>
+      <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="O26">
+        <v>5</v>
+      </c>
+      <c r="P26">
+        <v>5</v>
+      </c>
+      <c r="Q26">
+        <v>56</v>
+      </c>
+      <c r="R26">
+        <v>0</v>
+      </c>
+      <c r="S26">
+        <v>0</v>
+      </c>
+      <c r="T26">
+        <v>13</v>
+      </c>
+      <c r="U26">
+        <v>10</v>
+      </c>
+      <c r="V26">
+        <v>4</v>
+      </c>
+      <c r="W26">
+        <v>0</v>
+      </c>
+      <c r="X26">
+        <v>0</v>
+      </c>
+      <c r="Y26">
+        <v>0</v>
+      </c>
+      <c r="Z26">
+        <v>11</v>
+      </c>
+      <c r="AA26">
+        <v>4</v>
+      </c>
+      <c r="AB26">
+        <v>5</v>
+      </c>
+      <c r="AC26">
+        <v>5</v>
+      </c>
+      <c r="AD26">
+        <v>0</v>
+      </c>
+      <c r="AE26">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="str">
+        <v>LINE_ALBUM_Daily Sales Report B3(September)_261001_8.jpg</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>24/09/2026</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Thu</v>
+      </c>
+      <c r="C27">
+        <v>4911</v>
+      </c>
+      <c r="D27">
+        <v>3748</v>
+      </c>
+      <c r="E27">
+        <v>55</v>
+      </c>
+      <c r="F27">
+        <v>3693</v>
+      </c>
+      <c r="G27">
+        <v>1163</v>
+      </c>
+      <c r="H27">
+        <v>5</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>21</v>
+      </c>
+      <c r="K27">
+        <v>3</v>
+      </c>
+      <c r="L27">
+        <v>18</v>
+      </c>
+      <c r="M27">
+        <v>4</v>
+      </c>
+      <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="O27">
+        <v>3</v>
+      </c>
+      <c r="P27">
+        <v>6</v>
+      </c>
+      <c r="Q27">
+        <v>68</v>
+      </c>
+      <c r="R27">
+        <v>0</v>
+      </c>
+      <c r="S27">
+        <v>0</v>
+      </c>
+      <c r="T27">
+        <v>5</v>
+      </c>
+      <c r="U27">
+        <v>21</v>
+      </c>
+      <c r="V27">
+        <v>3</v>
+      </c>
+      <c r="W27">
+        <v>0</v>
+      </c>
+      <c r="X27">
+        <v>0</v>
+      </c>
+      <c r="Y27">
+        <v>0</v>
+      </c>
+      <c r="Z27">
+        <v>18</v>
+      </c>
+      <c r="AA27">
+        <v>4</v>
+      </c>
+      <c r="AB27">
+        <v>3</v>
+      </c>
+      <c r="AC27">
+        <v>6</v>
+      </c>
+      <c r="AD27">
+        <v>0</v>
+      </c>
+      <c r="AE27">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="str">
+        <v>LINE_ALBUM_Daily Sales Report B3(September)_261001_7.jpg</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>25/09/2026</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Fri</v>
+      </c>
+      <c r="C28">
+        <v>3236</v>
+      </c>
+      <c r="D28">
+        <v>2966</v>
+      </c>
+      <c r="E28">
+        <v>55</v>
+      </c>
+      <c r="F28">
+        <v>2911</v>
+      </c>
+      <c r="G28">
+        <v>270</v>
+      </c>
+      <c r="H28">
+        <v>7</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>5</v>
+      </c>
+      <c r="K28">
+        <v>1</v>
+      </c>
+      <c r="L28">
+        <v>5</v>
+      </c>
+      <c r="M28">
+        <v>3</v>
+      </c>
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="O28">
+        <v>3</v>
+      </c>
+      <c r="P28">
+        <v>8</v>
+      </c>
+      <c r="Q28">
+        <v>37</v>
+      </c>
+      <c r="R28">
+        <v>0</v>
+      </c>
+      <c r="S28">
+        <v>0</v>
+      </c>
+      <c r="T28">
+        <v>7</v>
+      </c>
+      <c r="U28">
+        <v>5</v>
+      </c>
+      <c r="V28">
+        <v>1</v>
+      </c>
+      <c r="W28">
+        <v>0</v>
+      </c>
+      <c r="X28">
+        <v>0</v>
+      </c>
+      <c r="Y28">
+        <v>0</v>
+      </c>
+      <c r="Z28">
+        <v>5</v>
+      </c>
+      <c r="AA28">
+        <v>3</v>
+      </c>
+      <c r="AB28">
+        <v>3</v>
+      </c>
+      <c r="AC28">
+        <v>8</v>
+      </c>
+      <c r="AD28">
+        <v>0</v>
+      </c>
+      <c r="AE28">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="str">
+        <v>LINE_ALBUM_Daily Sales Report B3(September)_261001_6.jpg</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>26/09/2026</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Sat</v>
+      </c>
+      <c r="C29">
+        <v>7077</v>
+      </c>
+      <c r="D29">
+        <v>6239</v>
+      </c>
+      <c r="E29">
+        <v>296</v>
+      </c>
+      <c r="F29">
+        <v>5943</v>
+      </c>
+      <c r="G29">
+        <v>838</v>
+      </c>
+      <c r="H29">
+        <v>17</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>19</v>
+      </c>
+      <c r="K29">
+        <v>11</v>
+      </c>
+      <c r="L29">
+        <v>15</v>
+      </c>
+      <c r="M29">
+        <v>4</v>
+      </c>
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="O29">
+        <v>10</v>
+      </c>
+      <c r="P29">
+        <v>5</v>
+      </c>
+      <c r="Q29">
+        <v>84</v>
+      </c>
+      <c r="R29">
+        <v>0</v>
+      </c>
+      <c r="S29">
+        <v>0</v>
+      </c>
+      <c r="T29">
+        <v>17</v>
+      </c>
+      <c r="U29">
+        <v>19</v>
+      </c>
+      <c r="V29">
+        <v>11</v>
+      </c>
+      <c r="W29">
+        <v>0</v>
+      </c>
+      <c r="X29">
+        <v>0</v>
+      </c>
+      <c r="Y29">
+        <v>0</v>
+      </c>
+      <c r="Z29">
+        <v>15</v>
+      </c>
+      <c r="AA29">
+        <v>4</v>
+      </c>
+      <c r="AB29">
+        <v>10</v>
+      </c>
+      <c r="AC29">
+        <v>5</v>
+      </c>
+      <c r="AD29">
+        <v>0</v>
+      </c>
+      <c r="AE29">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="str">
+        <v>LINE_ALBUM_Daily Sales Report B3(September)_261001_5.jpg</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>27/09/2026</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Sun</v>
+      </c>
+      <c r="C30">
+        <v>6847</v>
+      </c>
+      <c r="D30">
+        <v>6151</v>
+      </c>
+      <c r="E30">
+        <v>55</v>
+      </c>
+      <c r="F30">
+        <v>6096</v>
+      </c>
+      <c r="G30">
+        <v>696</v>
+      </c>
+      <c r="H30">
+        <v>8</v>
+      </c>
+      <c r="I30">
+        <v>1</v>
+      </c>
+      <c r="J30">
+        <v>18</v>
+      </c>
+      <c r="K30">
+        <v>7</v>
+      </c>
+      <c r="L30">
+        <v>15</v>
+      </c>
+      <c r="M30">
+        <v>2</v>
+      </c>
+      <c r="N30">
+        <v>0</v>
+      </c>
+      <c r="O30">
+        <v>7</v>
+      </c>
+      <c r="P30">
+        <v>7</v>
+      </c>
+      <c r="Q30">
+        <v>70</v>
+      </c>
+      <c r="R30">
+        <v>0</v>
+      </c>
+      <c r="S30">
+        <v>0</v>
+      </c>
+      <c r="T30">
+        <v>8</v>
+      </c>
+      <c r="U30">
+        <v>18</v>
+      </c>
+      <c r="V30">
+        <v>7</v>
+      </c>
+      <c r="W30">
+        <v>0</v>
+      </c>
+      <c r="X30">
+        <v>0</v>
+      </c>
+      <c r="Y30">
+        <v>0</v>
+      </c>
+      <c r="Z30">
+        <v>15</v>
+      </c>
+      <c r="AA30">
+        <v>2</v>
+      </c>
+      <c r="AB30">
+        <v>7</v>
+      </c>
+      <c r="AC30">
+        <v>7</v>
+      </c>
+      <c r="AD30">
+        <v>0</v>
+      </c>
+      <c r="AE30">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="str">
+        <v>LINE_ALBUM_Daily Sales Report B3(September)_261001_4.jpg</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>28/09/2026</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Mon</v>
+      </c>
+      <c r="C31">
+        <v>3696</v>
+      </c>
+      <c r="D31">
+        <v>2871</v>
+      </c>
+      <c r="E31">
+        <v>110</v>
+      </c>
+      <c r="F31">
+        <v>2761</v>
+      </c>
+      <c r="G31">
+        <v>825</v>
+      </c>
+      <c r="H31">
+        <v>9</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>4</v>
+      </c>
+      <c r="K31">
+        <v>6</v>
+      </c>
+      <c r="L31">
+        <v>17</v>
+      </c>
+      <c r="M31">
+        <v>0</v>
+      </c>
+      <c r="N31">
+        <v>0</v>
+      </c>
+      <c r="O31">
+        <v>2</v>
+      </c>
+      <c r="P31">
+        <v>3</v>
+      </c>
+      <c r="Q31">
+        <v>44</v>
+      </c>
+      <c r="R31">
+        <v>0</v>
+      </c>
+      <c r="S31">
+        <v>0</v>
+      </c>
+      <c r="T31">
+        <v>9</v>
+      </c>
+      <c r="U31">
+        <v>4</v>
+      </c>
+      <c r="V31">
+        <v>6</v>
+      </c>
+      <c r="W31">
+        <v>0</v>
+      </c>
+      <c r="X31">
+        <v>0</v>
+      </c>
+      <c r="Y31">
+        <v>0</v>
+      </c>
+      <c r="Z31">
+        <v>17</v>
+      </c>
+      <c r="AA31">
+        <v>0</v>
+      </c>
+      <c r="AB31">
+        <v>2</v>
+      </c>
+      <c r="AC31">
+        <v>3</v>
+      </c>
+      <c r="AD31">
+        <v>0</v>
+      </c>
+      <c r="AE31">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="str">
+        <v>LINE_ALBUM_Daily Sales Report B3(September)_261001_3.jpg</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>29/09/2026</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Tue</v>
+      </c>
+      <c r="C32">
+        <v>4589</v>
+      </c>
+      <c r="D32">
+        <v>4029</v>
+      </c>
+      <c r="E32">
+        <v>55</v>
+      </c>
+      <c r="F32">
+        <v>3974</v>
+      </c>
+      <c r="G32">
+        <v>560</v>
+      </c>
+      <c r="H32">
+        <v>6</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>12</v>
+      </c>
+      <c r="K32">
+        <v>6</v>
+      </c>
+      <c r="L32">
+        <v>10</v>
+      </c>
+      <c r="M32">
+        <v>5</v>
+      </c>
+      <c r="N32">
+        <v>0</v>
+      </c>
+      <c r="O32">
+        <v>6</v>
+      </c>
+      <c r="P32">
+        <v>5</v>
+      </c>
+      <c r="Q32">
+        <v>54</v>
+      </c>
+      <c r="R32">
+        <v>0</v>
+      </c>
+      <c r="S32">
+        <v>0</v>
+      </c>
+      <c r="T32">
+        <v>6</v>
+      </c>
+      <c r="U32">
+        <v>12</v>
+      </c>
+      <c r="V32">
+        <v>6</v>
+      </c>
+      <c r="W32">
+        <v>0</v>
+      </c>
+      <c r="X32">
+        <v>0</v>
+      </c>
+      <c r="Y32">
+        <v>0</v>
+      </c>
+      <c r="Z32">
+        <v>10</v>
+      </c>
+      <c r="AA32">
+        <v>5</v>
+      </c>
+      <c r="AB32">
+        <v>6</v>
+      </c>
+      <c r="AC32">
+        <v>5</v>
+      </c>
+      <c r="AD32">
+        <v>0</v>
+      </c>
+      <c r="AE32">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="str">
+        <v>LINE_ALBUM_Daily Sales Report B3(September)_261001_2.jpg</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>30/09/2026</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Wed</v>
+      </c>
+      <c r="C33">
+        <v>5466</v>
+      </c>
+      <c r="D33">
+        <v>4238</v>
+      </c>
+      <c r="E33">
+        <v>55</v>
+      </c>
+      <c r="F33">
+        <v>4183</v>
+      </c>
+      <c r="G33">
+        <v>1228</v>
+      </c>
+      <c r="H33">
+        <v>8</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>17</v>
+      </c>
+      <c r="K33">
+        <v>8</v>
+      </c>
+      <c r="L33">
+        <v>17</v>
+      </c>
+      <c r="M33">
+        <v>1</v>
+      </c>
+      <c r="N33">
+        <v>0</v>
+      </c>
+      <c r="O33">
+        <v>5</v>
+      </c>
+      <c r="P33">
+        <v>5</v>
+      </c>
+      <c r="Q33">
+        <v>64</v>
+      </c>
+      <c r="R33">
+        <v>0</v>
+      </c>
+      <c r="S33">
+        <v>0</v>
+      </c>
+      <c r="T33">
+        <v>8</v>
+      </c>
+      <c r="U33">
+        <v>17</v>
+      </c>
+      <c r="V33">
+        <v>8</v>
+      </c>
+      <c r="W33">
+        <v>0</v>
+      </c>
+      <c r="X33">
+        <v>0</v>
+      </c>
+      <c r="Y33">
+        <v>0</v>
+      </c>
+      <c r="Z33">
+        <v>17</v>
+      </c>
+      <c r="AA33">
+        <v>1</v>
+      </c>
+      <c r="AB33">
+        <v>5</v>
+      </c>
+      <c r="AC33">
+        <v>5</v>
+      </c>
+      <c r="AD33">
+        <v>0</v>
+      </c>
+      <c r="AE33">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="str">
+        <v>LINE_ALBUM_Daily Sales Report B3(September)_261001_1.jpg</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AD2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AF33"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/3_Automation_Dashboard/SomSaiJai_Dashboard_B3_2026.xlsx
+++ b/3_Automation_Dashboard/SomSaiJai_Dashboard_B3_2026.xlsx
@@ -3344,10 +3344,10 @@
         <v>Other OPEX</v>
       </c>
       <c r="E31" t="str">
-        <v>ค่าขนส่ง / logistics / supplies Sep (B3 portion 45.10%)</v>
+        <v>ค่าขนส่ง / logistics / supplies Sep (B3 portion 44.30%)</v>
       </c>
       <c r="F31">
-        <v>5592.59</v>
+        <v>5492.65</v>
       </c>
     </row>
   </sheetData>

--- a/3_Automation_Dashboard/SomSaiJai_Dashboard_B3_2026.xlsx
+++ b/3_Automation_Dashboard/SomSaiJai_Dashboard_B3_2026.xlsx
@@ -133,10 +133,10 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Jpan" typeface="ï¼­ï¼³ ï¼°ã´ã·ãã¯"/>
+        <a:font script="Hang" typeface="ë§ì ê³ ë"/>
+        <a:font script="Hans" typeface="å®ä½"/>
+        <a:font script="Hant" typeface="æ°ç´°æé«"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -168,10 +168,10 @@
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Jpan" typeface="ï¼­ï¼³ ï¼°ã´ã·ãã¯"/>
+        <a:font script="Hang" typeface="ë§ì ê³ ë"/>
+        <a:font script="Hans" typeface="å®ä½"/>
+        <a:font script="Hant" typeface="æ°ç´°æé«"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -2449,7 +2449,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AD2"/>
+  <dimension ref="A1:AE3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2547,10 +2547,36 @@
       <c r="AD2" t="str">
         <v>Used Young Coco</v>
       </c>
+      <c r="AE2" t="str">
+        <v>Source Note</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>14/10/2026</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Wed</v>
+      </c>
+      <c r="C3">
+        <v>6821</v>
+      </c>
+      <c r="D3">
+        <v>5361</v>
+      </c>
+      <c r="E3">
+        <v>55</v>
+      </c>
+      <c r="G3">
+        <v>1460</v>
+      </c>
+      <c r="AE3" t="str">
+        <v>LINE set_single636550441915908205 sha256:18fe5952773c | some cup counts were uncertain and were not written</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AD2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AE3"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/3_Automation_Dashboard/SomSaiJai_Dashboard_B3_2026.xlsx
+++ b/3_Automation_Dashboard/SomSaiJai_Dashboard_B3_2026.xlsx
@@ -133,10 +133,10 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ï¼­ï¼³ ï¼°ã´ã·ãã¯"/>
-        <a:font script="Hang" typeface="ë§ì ê³ ë"/>
-        <a:font script="Hans" typeface="å®ä½"/>
-        <a:font script="Hant" typeface="æ°ç´°æé«"/>
+        <a:font script="Jpan" typeface="Ã¯Â¼Â­Ã¯Â¼Â³ Ã¯Â¼Â°Ã£ÂÂ´Ã£ÂÂ·Ã£ÂÂÃ£ÂÂ¯"/>
+        <a:font script="Hang" typeface="Ã«Â§ÂÃ¬ÂÂ ÃªÂ³Â Ã«ÂÂ"/>
+        <a:font script="Hans" typeface="Ã¥Â®ÂÃ¤Â½Â"/>
+        <a:font script="Hant" typeface="Ã¦ÂÂ°Ã§Â´Â°Ã¦ÂÂÃ©Â«Â"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -168,10 +168,10 @@
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ï¼­ï¼³ ï¼°ã´ã·ãã¯"/>
-        <a:font script="Hang" typeface="ë§ì ê³ ë"/>
-        <a:font script="Hans" typeface="å®ä½"/>
-        <a:font script="Hant" typeface="æ°ç´°æé«"/>
+        <a:font script="Jpan" typeface="Ã¯Â¼Â­Ã¯Â¼Â³ Ã¯Â¼Â°Ã£ÂÂ´Ã£ÂÂ·Ã£ÂÂÃ£ÂÂ¯"/>
+        <a:font script="Hang" typeface="Ã«Â§ÂÃ¬ÂÂ ÃªÂ³Â Ã«ÂÂ"/>
+        <a:font script="Hans" typeface="Ã¥Â®ÂÃ¤Â½Â"/>
+        <a:font script="Hant" typeface="Ã¦ÂÂ°Ã§Â´Â°Ã¦ÂÂÃ©Â«Â"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -2449,7 +2449,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE3"/>
+  <dimension ref="A1:AE17"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2574,9 +2574,709 @@
         <v>LINE set_single636550441915908205 sha256:18fe5952773c | some cup counts were uncertain and were not written</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>01/10/2026</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Thu</v>
+      </c>
+      <c r="C4">
+        <v>4586</v>
+      </c>
+      <c r="D4">
+        <v>3654</v>
+      </c>
+      <c r="E4">
+        <v>55</v>
+      </c>
+      <c r="G4">
+        <v>932</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>16</v>
+      </c>
+      <c r="K4">
+        <v>4</v>
+      </c>
+      <c r="L4">
+        <v>15</v>
+      </c>
+      <c r="M4">
+        <v>4</v>
+      </c>
+      <c r="O4">
+        <v>4</v>
+      </c>
+      <c r="P4">
+        <v>1</v>
+      </c>
+      <c r="Q4">
+        <v>56</v>
+      </c>
+      <c r="AE4" t="str">
+        <v>Parn LINE photo 2a99558801b9 (B3 Daily Shop Report), hand-transcribed 2026-10-18 | not in fruit columns: Mangosteen Blended 8, Rambutan Blended 2, Mango Sticky Rice 1, Mango Sticky Rice (180) 1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>02/10/2026</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Fri</v>
+      </c>
+      <c r="C5">
+        <v>6786</v>
+      </c>
+      <c r="D5">
+        <v>4851</v>
+      </c>
+      <c r="E5">
+        <v>110</v>
+      </c>
+      <c r="G5">
+        <v>1935</v>
+      </c>
+      <c r="H5">
+        <v>5</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>17</v>
+      </c>
+      <c r="K5">
+        <v>12</v>
+      </c>
+      <c r="L5">
+        <v>10</v>
+      </c>
+      <c r="M5">
+        <v>8</v>
+      </c>
+      <c r="O5">
+        <v>8</v>
+      </c>
+      <c r="P5">
+        <v>7</v>
+      </c>
+      <c r="Q5">
+        <v>76</v>
+      </c>
+      <c r="AE5" t="str">
+        <v>Parn LINE photo 304767194108 (B3 Daily Shop Report), hand-transcribed 2026-10-18 | not in fruit columns: Mangosteen Lychee Blended 4, Mango Sticky Rice 2, Cold Pressed Mango Juice 3 | CHECK: items 6876 vs total sales 6786 (+90)</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>03/10/2026</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Sat</v>
+      </c>
+      <c r="C6">
+        <v>6623</v>
+      </c>
+      <c r="D6">
+        <v>3899</v>
+      </c>
+      <c r="E6">
+        <v>55</v>
+      </c>
+      <c r="G6">
+        <v>2724</v>
+      </c>
+      <c r="H6">
+        <v>14</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>15</v>
+      </c>
+      <c r="K6">
+        <v>8</v>
+      </c>
+      <c r="L6">
+        <v>15</v>
+      </c>
+      <c r="M6">
+        <v>11</v>
+      </c>
+      <c r="O6">
+        <v>1</v>
+      </c>
+      <c r="P6">
+        <v>8</v>
+      </c>
+      <c r="Q6">
+        <v>80</v>
+      </c>
+      <c r="AE6" t="str">
+        <v>Parn LINE photo c4bc76799df9 (B3 Daily Shop Report), hand-transcribed 2026-10-18 | not in fruit columns: Mangosteen Blended 4, Mangosteen Lychee Blended 1, Volcano Mix Fruit 1, Mango Sticky Rice 1, Mango Sticky Rice (180) 1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>04/10/2026</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Sun</v>
+      </c>
+      <c r="C7">
+        <v>9583</v>
+      </c>
+      <c r="D7">
+        <v>6269</v>
+      </c>
+      <c r="E7">
+        <v>254</v>
+      </c>
+      <c r="G7">
+        <v>3314</v>
+      </c>
+      <c r="H7">
+        <v>15</v>
+      </c>
+      <c r="I7">
+        <v>2</v>
+      </c>
+      <c r="J7">
+        <v>29</v>
+      </c>
+      <c r="K7">
+        <v>7</v>
+      </c>
+      <c r="L7">
+        <v>31</v>
+      </c>
+      <c r="M7">
+        <v>11</v>
+      </c>
+      <c r="O7">
+        <v>8</v>
+      </c>
+      <c r="P7">
+        <v>5</v>
+      </c>
+      <c r="Q7">
+        <v>123</v>
+      </c>
+      <c r="AE7" t="str">
+        <v>Parn LINE photo 0167ca668ee7 (B3 Daily Shop Report), hand-transcribed 2026-10-18 | exp incl. Condensed Milk 144 | not in fruit columns: Mangosteen Blended 1, Mangosteen Lychee Blended 4, Mango Sticky Rice 5, Mango Sticky Rice (180) 1, Pomegranate 4 | CHECK: items 9760 vs total sales 9583 (+177)</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>05/10/2026</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Mon</v>
+      </c>
+      <c r="C8">
+        <v>4848</v>
+      </c>
+      <c r="D8">
+        <v>3083</v>
+      </c>
+      <c r="E8">
+        <v>251</v>
+      </c>
+      <c r="G8">
+        <v>1765</v>
+      </c>
+      <c r="H8">
+        <v>9</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>14</v>
+      </c>
+      <c r="K8">
+        <v>7</v>
+      </c>
+      <c r="L8">
+        <v>9</v>
+      </c>
+      <c r="M8">
+        <v>3</v>
+      </c>
+      <c r="O8">
+        <v>3</v>
+      </c>
+      <c r="P8">
+        <v>1</v>
+      </c>
+      <c r="Q8">
+        <v>51</v>
+      </c>
+      <c r="AE8" t="str">
+        <v>Parn LINE photo 95b4be4f1f66 (B3 Daily Shop Report), hand-transcribed 2026-10-18 | exp incl. Meiji Milk 72, Falcon (2) 124 | not in fruit columns: Mangosteen Blended 1, Volcano Mix Fruit 1, Pomegranate 3 | CHECK: items 4847 vs total sales 4848 (-1)</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>06/10/2026</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Tue</v>
+      </c>
+      <c r="C9">
+        <v>4280</v>
+      </c>
+      <c r="D9">
+        <v>3023</v>
+      </c>
+      <c r="E9">
+        <v>110</v>
+      </c>
+      <c r="G9">
+        <v>1257</v>
+      </c>
+      <c r="H9">
+        <v>4</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>10</v>
+      </c>
+      <c r="K9">
+        <v>2</v>
+      </c>
+      <c r="L9">
+        <v>19</v>
+      </c>
+      <c r="M9">
+        <v>7</v>
+      </c>
+      <c r="O9">
+        <v>3</v>
+      </c>
+      <c r="P9">
+        <v>3</v>
+      </c>
+      <c r="Q9">
+        <v>56</v>
+      </c>
+      <c r="AE9" t="str">
+        <v>Parn LINE photo 986ac49e9396 (B3 Daily Shop Report), hand-transcribed 2026-10-18 | not in fruit columns: Grape 3, Volcano Mix Fruit 2, Pear 2, Pomegranate 1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>07/10/2026</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Wed</v>
+      </c>
+      <c r="C10">
+        <v>4737</v>
+      </c>
+      <c r="D10">
+        <v>3407</v>
+      </c>
+      <c r="E10">
+        <v>55</v>
+      </c>
+      <c r="G10">
+        <v>1330</v>
+      </c>
+      <c r="H10">
+        <v>8</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>15</v>
+      </c>
+      <c r="K10">
+        <v>5</v>
+      </c>
+      <c r="L10">
+        <v>6</v>
+      </c>
+      <c r="M10">
+        <v>6</v>
+      </c>
+      <c r="O10">
+        <v>4</v>
+      </c>
+      <c r="P10">
+        <v>4</v>
+      </c>
+      <c r="Q10">
+        <v>58</v>
+      </c>
+      <c r="AE10" t="str">
+        <v>Parn LINE photo 6e3fa4cccd28 (B3 Daily Shop Report), hand-transcribed 2026-10-18 | not in fruit columns: Grape 3, Pear 1, Volcano Mix Fruit 1, Pomegranate 5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>08/10/2026</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Thu</v>
+      </c>
+      <c r="C11">
+        <v>6569</v>
+      </c>
+      <c r="D11">
+        <v>4377</v>
+      </c>
+      <c r="E11">
+        <v>55</v>
+      </c>
+      <c r="G11">
+        <v>2192</v>
+      </c>
+      <c r="H11">
+        <v>5</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>29</v>
+      </c>
+      <c r="K11">
+        <v>6</v>
+      </c>
+      <c r="L11">
+        <v>19</v>
+      </c>
+      <c r="M11">
+        <v>9</v>
+      </c>
+      <c r="O11">
+        <v>5</v>
+      </c>
+      <c r="P11">
+        <v>2</v>
+      </c>
+      <c r="Q11">
+        <v>87</v>
+      </c>
+      <c r="AE11" t="str">
+        <v>Parn LINE photo 280755341c77 (B3 Daily Shop Report), hand-transcribed 2026-10-18 | not in fruit columns: Pomegranate 2, Mangosteen Lychee Blended 6, Pear 1, Grape 3 | CHECK: items 6520 vs total sales 6569 (-49)</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>09/10/2026</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Fri</v>
+      </c>
+      <c r="C12">
+        <v>9383</v>
+      </c>
+      <c r="D12">
+        <v>6973</v>
+      </c>
+      <c r="E12">
+        <v>110</v>
+      </c>
+      <c r="G12">
+        <v>2410</v>
+      </c>
+      <c r="H12">
+        <v>17</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+      <c r="J12">
+        <v>24</v>
+      </c>
+      <c r="K12">
+        <v>14</v>
+      </c>
+      <c r="L12">
+        <v>15</v>
+      </c>
+      <c r="M12">
+        <v>8</v>
+      </c>
+      <c r="O12">
+        <v>14</v>
+      </c>
+      <c r="P12">
+        <v>5</v>
+      </c>
+      <c r="Q12">
+        <v>110</v>
+      </c>
+      <c r="AE12" t="str">
+        <v>Parn LINE photo 4714870e0a9d (B3 Daily Shop Report), hand-transcribed 2026-10-18 | not in fruit columns: Pear 2, Grape 6, Pomegranate 3, Volcano Mix Fruit 1 | CHECK: items 9315 vs total sales 9383 (-68)</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>11/10/2026</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Sun</v>
+      </c>
+      <c r="C13">
+        <v>6874</v>
+      </c>
+      <c r="D13">
+        <v>4290</v>
+      </c>
+      <c r="E13">
+        <v>55</v>
+      </c>
+      <c r="G13">
+        <v>2584</v>
+      </c>
+      <c r="H13">
+        <v>15</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>19</v>
+      </c>
+      <c r="K13">
+        <v>9</v>
+      </c>
+      <c r="L13">
+        <v>16</v>
+      </c>
+      <c r="M13">
+        <v>8</v>
+      </c>
+      <c r="O13">
+        <v>8</v>
+      </c>
+      <c r="P13">
+        <v>0</v>
+      </c>
+      <c r="Q13">
+        <v>87</v>
+      </c>
+      <c r="AE13" t="str">
+        <v>Parn LINE photo 413bb3937c75 (B3 Daily Shop Report), hand-transcribed 2026-10-18 | not in fruit columns: Pear 5, Mangosteen Lychee Blended 3, Pomegranate 3, Mango Sticky Rice (180) 1 | CHECK: items 6789 vs total sales 6874 (-85)</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>12/10/2026</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Mon</v>
+      </c>
+      <c r="C14">
+        <v>6118</v>
+      </c>
+      <c r="D14">
+        <v>4581</v>
+      </c>
+      <c r="E14">
+        <v>110</v>
+      </c>
+      <c r="G14">
+        <v>1537</v>
+      </c>
+      <c r="H14">
+        <v>7</v>
+      </c>
+      <c r="I14">
+        <v>1</v>
+      </c>
+      <c r="J14">
+        <v>13</v>
+      </c>
+      <c r="K14">
+        <v>11</v>
+      </c>
+      <c r="L14">
+        <v>15</v>
+      </c>
+      <c r="M14">
+        <v>4</v>
+      </c>
+      <c r="O14">
+        <v>6</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="Q14">
+        <v>71</v>
+      </c>
+      <c r="AE14" t="str">
+        <v>Parn LINE photo abc0ad7c829d (B3 Daily Shop Report), hand-transcribed 2026-10-18 | not in fruit columns: Mangosteen Lychee Blended 4, Pomegranate 7, Grape 3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>13/10/2026</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Tue</v>
+      </c>
+      <c r="C15">
+        <v>8873</v>
+      </c>
+      <c r="D15">
+        <v>5531</v>
+      </c>
+      <c r="E15">
+        <v>110</v>
+      </c>
+      <c r="G15">
+        <v>3342</v>
+      </c>
+      <c r="H15">
+        <v>9</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>26</v>
+      </c>
+      <c r="K15">
+        <v>19</v>
+      </c>
+      <c r="L15">
+        <v>18</v>
+      </c>
+      <c r="M15">
+        <v>10</v>
+      </c>
+      <c r="O15">
+        <v>8</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
+      </c>
+      <c r="Q15">
+        <v>108</v>
+      </c>
+      <c r="AE15" t="str">
+        <v>Parn LINE photo fe9dd0f63e63 (B3 Daily Shop Report), hand-transcribed 2026-10-18 | not in fruit columns: Apple &amp; Pear 8, Mangosteen Blended 1, Mangosteen Lychee Blended 4, Pomegranate 1, Grape 4 | CHECK: items 8874 vs total sales 8873 (+1)</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>15/10/2026</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Thu</v>
+      </c>
+      <c r="C16">
+        <v>5667</v>
+      </c>
+      <c r="D16">
+        <v>4202</v>
+      </c>
+      <c r="E16">
+        <v>110</v>
+      </c>
+      <c r="G16">
+        <v>1465</v>
+      </c>
+      <c r="H16">
+        <v>9</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>7</v>
+      </c>
+      <c r="K16">
+        <v>13</v>
+      </c>
+      <c r="L16">
+        <v>18</v>
+      </c>
+      <c r="M16">
+        <v>3</v>
+      </c>
+      <c r="O16">
+        <v>4</v>
+      </c>
+      <c r="P16">
+        <v>0</v>
+      </c>
+      <c r="Q16">
+        <v>68</v>
+      </c>
+      <c r="AE16" t="str">
+        <v>Parn LINE photo f918b3f949df (B3 Daily Shop Report), hand-transcribed 2026-10-18 | not in fruit columns: Pear 4, Mangosteen Lychee Blended 4, Pomegranate 5, Grape 1 | CHECK: items 5664 vs total sales 5667 (-3)</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>16/10/2026</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Fri</v>
+      </c>
+      <c r="C17">
+        <v>5672</v>
+      </c>
+      <c r="D17">
+        <v>4328</v>
+      </c>
+      <c r="E17">
+        <v>55</v>
+      </c>
+      <c r="G17">
+        <v>1344</v>
+      </c>
+      <c r="H17">
+        <v>11</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>12</v>
+      </c>
+      <c r="K17">
+        <v>4</v>
+      </c>
+      <c r="L17">
+        <v>14</v>
+      </c>
+      <c r="M17">
+        <v>4</v>
+      </c>
+      <c r="O17">
+        <v>7</v>
+      </c>
+      <c r="P17">
+        <v>0</v>
+      </c>
+      <c r="Q17">
+        <v>65</v>
+      </c>
+      <c r="AE17" t="str">
+        <v>Parn LINE photo 75e2ab1664c2 (B3 Daily Shop Report), hand-transcribed 2026-10-18 | not in fruit columns: Pomegranate 3, Mangosteen Lychee Blended 6, Volcano Mix Fruit 1, Pear 1, Grape 2 | CHECK: items 5617 vs total sales 5672 (-55)</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AE3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AE17"/>
   </ignoredErrors>
 </worksheet>
 </file>
